--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:46</t>
+    <t xml:space="preserve">2026-09-09 20:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:08</t>
+    <t xml:space="preserve">2026-09-18 17:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_maule.xlsx
@@ -30,96 +30,96 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelluhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curepto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualañé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colbún</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Clemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alegre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Javier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maule</t>
   </si>
   <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Javier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alegre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Clemente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colbún</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curepto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pencahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelluhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:05</t>
+    <t xml:space="preserve">2026-09-27 21:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -549,13 +549,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>52324</v>
+        <v>13019</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>64676</v>
+        <v>10189</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>80.9</v>
+        <v>127.78</v>
       </c>
     </row>
     <row r="3">
@@ -563,13 +563,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3982</v>
+        <v>11734</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4194</v>
+        <v>9253</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>94.95</v>
+        <v>126.81</v>
       </c>
     </row>
     <row r="4">
@@ -577,13 +577,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11263</v>
+        <v>10341</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11510</v>
+        <v>8276</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>97.85</v>
+        <v>124.95</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>50318</v>
+        <v>10602</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>50983</v>
+        <v>8622</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>98.7</v>
+        <v>122.96</v>
       </c>
     </row>
     <row r="6">
@@ -605,13 +605,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>238070</v>
+        <v>19499</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>239735</v>
+        <v>16557</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>99.31</v>
+        <v>117.77</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>19652</v>
+        <v>10763</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>19515</v>
+        <v>9285</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>100.7</v>
+        <v>115.92</v>
       </c>
     </row>
     <row r="8">
@@ -633,13 +633,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>31615</v>
+        <v>11687</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>31390</v>
+        <v>10232</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>100.72</v>
+        <v>114.22</v>
       </c>
     </row>
     <row r="9">
@@ -647,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>169710</v>
+        <v>36603</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>167746</v>
+        <v>33264</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>101.17</v>
+        <v>110.04</v>
       </c>
     </row>
     <row r="10">
@@ -661,13 +661,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>51318</v>
+        <v>4766</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>50496</v>
+        <v>4347</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>101.63</v>
+        <v>109.64</v>
       </c>
     </row>
     <row r="11">
@@ -675,13 +675,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>18089</v>
+        <v>16355</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>17787</v>
+        <v>14952</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>101.7</v>
+        <v>109.38</v>
       </c>
     </row>
     <row r="12">
@@ -689,13 +689,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>52235</v>
+        <v>48671</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>50547</v>
+        <v>45103</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>103.34</v>
+        <v>107.91</v>
       </c>
     </row>
     <row r="13">
@@ -703,13 +703,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>49099</v>
+        <v>7534</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>47177</v>
+        <v>6993</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>104.07</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="14">
@@ -717,13 +717,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9703</v>
+        <v>47049</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>9299</v>
+        <v>44327</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>104.34</v>
+        <v>106.14</v>
       </c>
     </row>
     <row r="15">
@@ -731,13 +731,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>22319</v>
+        <v>24419</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>21299</v>
+        <v>23042</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>104.79</v>
+        <v>105.98</v>
       </c>
     </row>
     <row r="16">
@@ -745,13 +745,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>20670</v>
+        <v>108121</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>19627</v>
+        <v>102620</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>105.31</v>
+        <v>105.36</v>
       </c>
     </row>
     <row r="17">
@@ -759,13 +759,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>108121</v>
+        <v>20670</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>102620</v>
+        <v>19627</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>105.36</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="18">
@@ -773,13 +773,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>24419</v>
+        <v>22319</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>23042</v>
+        <v>21299</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>105.98</v>
+        <v>104.79</v>
       </c>
     </row>
     <row r="19">
@@ -787,13 +787,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>47049</v>
+        <v>9703</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>44327</v>
+        <v>9299</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>106.14</v>
+        <v>104.34</v>
       </c>
     </row>
     <row r="20">
@@ -801,13 +801,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7534</v>
+        <v>49099</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6993</v>
+        <v>47177</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>107.74</v>
+        <v>104.07</v>
       </c>
     </row>
     <row r="21">
@@ -815,13 +815,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>48671</v>
+        <v>52235</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>45103</v>
+        <v>50547</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>107.91</v>
+        <v>103.34</v>
       </c>
     </row>
     <row r="22">
@@ -829,13 +829,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>16355</v>
+        <v>18089</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>14952</v>
+        <v>17787</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>109.38</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="23">
@@ -843,13 +843,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>4766</v>
+        <v>51318</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>4347</v>
+        <v>50496</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>109.64</v>
+        <v>101.63</v>
       </c>
     </row>
     <row r="24">
@@ -857,13 +857,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>36603</v>
+        <v>169710</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>33264</v>
+        <v>167746</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>110.04</v>
+        <v>101.17</v>
       </c>
     </row>
     <row r="25">
@@ -871,13 +871,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>11687</v>
+        <v>31615</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>10232</v>
+        <v>31390</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>114.22</v>
+        <v>100.72</v>
       </c>
     </row>
     <row r="26">
@@ -885,13 +885,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>10763</v>
+        <v>19652</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>9285</v>
+        <v>19515</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>115.92</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="27">
@@ -899,13 +899,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>19499</v>
+        <v>238070</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>16557</v>
+        <v>239735</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>117.77</v>
+        <v>99.31</v>
       </c>
     </row>
     <row r="28">
@@ -913,13 +913,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>10602</v>
+        <v>50318</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8622</v>
+        <v>50983</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>122.96</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="29">
@@ -927,13 +927,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>10341</v>
+        <v>11263</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>8276</v>
+        <v>11510</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>124.95</v>
+        <v>97.85</v>
       </c>
     </row>
     <row r="30">
@@ -941,13 +941,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>11734</v>
+        <v>3982</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9253</v>
+        <v>4194</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>126.81</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="31">
@@ -955,13 +955,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>13019</v>
+        <v>52324</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>10189</v>
+        <v>64676</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>127.78</v>
+        <v>80.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_maule.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:51</t>
+    <t xml:space="preserve">2026-10-05 05:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
